--- a/samples/Prepaid_Committee_2025.xlsx
+++ b/samples/Prepaid_Committee_2025.xlsx
@@ -892,7 +892,7 @@
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,370,000</t>
         </is>
       </c>
       <c r="O7" s="9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>$7.2B</t>
+          <t>$7.19B</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr"/>
@@ -973,7 +973,7 @@
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O8" s="9" t="inlineStr">
@@ -1004,12 +1004,28 @@
           <t>1998</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Yes (legislative)</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Yes (in state only)</t>
+        </is>
+      </c>
       <c r="F9" s="8" t="inlineStr"/>
       <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="9" t="inlineStr"/>
-      <c r="I9" s="9" t="inlineStr"/>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>3% for next 3 years, then 5% for next 5 years</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
       <c r="J9" s="9" t="inlineStr"/>
       <c r="K9" s="9" t="n">
         <v/>
@@ -1088,7 +1104,7 @@
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>MET I: $105.7M  MET II: $1.1B</t>
+          <t>MET I: $105.7M  MET II: $1.08B</t>
         </is>
       </c>
       <c r="N10" s="9" t="inlineStr">
@@ -1102,7 +1118,11 @@
         </is>
       </c>
       <c r="P10" s="9" t="inlineStr"/>
-      <c r="Q10" s="9" t="inlineStr"/>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>All data is as of 9/30/25</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -1150,8 +1170,10 @@
           <t>Horizon: 5.5% Legacy: 5.5%</t>
         </is>
       </c>
-      <c r="J11" s="10" t="n">
-        <v>1.4</v>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>Horizon: 140.0%  Legacy: 106%</t>
+        </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
@@ -1342,7 +1364,7 @@
       </c>
       <c r="P13" s="9" t="inlineStr">
         <is>
-          <t>$3.8B</t>
+          <t>$3.82B</t>
         </is>
       </c>
       <c r="Q13" s="9" t="inlineStr">
@@ -1412,7 +1434,7 @@
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>$1.3B</t>
+          <t>$1.33B</t>
         </is>
       </c>
       <c r="N14" s="9" t="inlineStr">
@@ -1512,7 +1534,7 @@
       </c>
       <c r="P15" s="9" t="inlineStr">
         <is>
-          <t>$3.0B</t>
+          <t>$3.03B</t>
         </is>
       </c>
       <c r="Q15" s="9" t="inlineStr"/>
@@ -1578,7 +1600,7 @@
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>$1.9B</t>
+          <t>$1.89B</t>
         </is>
       </c>
       <c r="N16" s="9" t="inlineStr">
@@ -1786,7 +1808,7 @@
       </c>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>$1.3B</t>
+          <t>$1.348B</t>
         </is>
       </c>
       <c r="Q19" s="9" t="inlineStr"/>
@@ -1867,7 +1889,7 @@
       </c>
       <c r="P20" s="9" t="inlineStr">
         <is>
-          <t>$1.8B</t>
+          <t>$1.75B</t>
         </is>
       </c>
       <c r="Q20" s="9" t="inlineStr">
@@ -2207,7 +2229,7 @@
       </c>
       <c r="P24" s="9" t="inlineStr">
         <is>
-          <t>$2.6B</t>
+          <t>$2.62B</t>
         </is>
       </c>
       <c r="Q24" s="9" t="inlineStr">
